--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>46281</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44879</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45825</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45356</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>45735</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>46038</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46135</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>46133</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45832</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>45224</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>44831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>45321</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>45971</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>46051</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>46245</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46121</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45146</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45159</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>44596</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>46279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45812</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45209</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45730</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>44663</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44483</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44483</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44698</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44749</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44469</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44512</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>44901</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>45132</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>45687</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>45089</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>44942</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>45057</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44532</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>44802</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44774</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>45098</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45278</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44726</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45630</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45135</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45182</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45231</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45688</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>45377</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>44846</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45264</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44909</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45734</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44928</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44469</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45362</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45719</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44981</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45385</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44501</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45215</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45582</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45076</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45274</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44753</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45693</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44810</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44810</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45603</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45440</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44949</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45098</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44901</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44984</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45385</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45071</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45020</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44929</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45670</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44600</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45603</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45349</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44603</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44909</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45849</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45562</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44865</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45483</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45680</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>44943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44882</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>45320</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45818</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45232</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45211</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45812</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45139</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44467</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45707</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45905</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45905</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45905</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45644</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45587</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45195</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45299</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44883</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45206</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45918</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45385</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>45918</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45834</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45426</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>46142</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45519</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45098</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44501</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45453</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45327</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45617</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>46151</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45582</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45625</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45166</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45959</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44600</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45658</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44930</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45327</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45971</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45971</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45020</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45769</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45377</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46030</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45973</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45131</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45614</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45727</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45685</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45320</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45230</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45179</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44902</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45119</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45688</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45327</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46006</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45628</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44511</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>46009</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46009</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45035</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45994</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>45699</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44869</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>44869</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>45002</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44873</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44895</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45646</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46034</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>46174</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>46034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45849</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45219</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44771</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44873</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46174</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>46174</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46174</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>46038</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44922</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44463</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44827</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>44949</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>46048</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45232</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45171</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44467</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>46052</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45841</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44572</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46056</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46056</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>46057</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45364</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44462</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45006</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45006</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44594</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44525</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46078</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46184</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45195</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45239</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45320</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46188</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>44677</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45994</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45195</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45349</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45230</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>44600</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>46091</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>46094</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>46093</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45589</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>46191</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46196</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>46196</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>46098</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46106</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>46105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>46105</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45126</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45069</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45314</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>46111</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>46202</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45643</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>46113</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45119</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>46121</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>46209</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>46202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>44855</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45208</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45139</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45139</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>45314</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>46133</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44639</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>44943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>45342</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45342</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44810</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45054</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>46246</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44511</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>46135</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>46134</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45531</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>44602</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44902</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45035</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45337</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45845</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45268</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45112</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45112</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>46246</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45027</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45040</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45747</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45135</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45603</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45734</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46246</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45707</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44909</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45357</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45581</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>46206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46251</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>46206</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45303</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45582</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>46253</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45474</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45022</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>46211</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>46209</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>46209</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>44726</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27783,7 +27783,7 @@
         <v>46066</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45075</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45159</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45239</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45544</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45603</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45364</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>46255</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45239</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45337</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45152</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46259</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>45076</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45317</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45156</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>45278</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>45603</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>45006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>46222</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>45762</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45130</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>46050</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>44491</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45646</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45415</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45548</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>46269</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45758</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>46135</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46272</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45646</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45246</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>46279</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45576</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45957</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45538</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45981</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>46237</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45695</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45273</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45587</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45644</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46237</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45000</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46171</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46255</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45171</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45825</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45842</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45843</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45842</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45299</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45849</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45849</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45849</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45734</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45802</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45322</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>45156</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45635</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45555</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45555</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45555</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44977</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45554</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>45545</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45695</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45730</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45730</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45096</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45168</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45275</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45170</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45089</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45485</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45792</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45824</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>44902</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>44951</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45343</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45222</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>44645</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45751</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>44483</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>44553</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>44880</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45184</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45104</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44964</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44964</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45450</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45275</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44517</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45156</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45093</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45104</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45826</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>44909</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45363</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45147</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44951</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45070</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>44977</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>45442</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>44992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>44995</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>44517</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>44931</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45635</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45799</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45880</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45950</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46035</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>46072</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>46091</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46091</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>46091</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>46094</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>46098</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44973</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45825</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44879</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44846</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46038</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>46135</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>46051</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46121</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45971</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45730</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>45224</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46245</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46290</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45159</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44663</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44483</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>44483</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44749</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44469</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44512</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45625</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45734</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45327</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45688</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>45195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45208</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45364</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45135</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44771</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45219</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45362</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44810</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44810</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44467</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45239</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45239</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44869</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>46034</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>46034</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44467</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45020</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45818</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44928</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45337</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>46038</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45483</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44855</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44873</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>46048</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45903</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45841</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45905</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45905</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46052</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46056</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45548</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45553</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44639</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>46057</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45918</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>45603</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45918</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44600</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45364</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45834</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>46078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45320</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45239</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44943</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>46093</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46091</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45587</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45589</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46094</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>46098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45377</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45089</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>46105</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45006</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>46105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>44895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45282</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>46113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44831</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45628</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>46121</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44469</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>46122</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45965</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45971</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45973</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45002</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45979</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45646</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46134</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>46133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45849</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45582</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>46135</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45845</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44902</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45994</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45076</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45693</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45027</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45035</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45707</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45171</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44846</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45544</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45680</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46006</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>46009</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45727</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>46009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45994</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45006</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45188</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45644</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45769</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45687</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45700</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44902</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>44603</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45299</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45474</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44928</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46151</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45253</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45385</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45278</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45342</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45342</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45614</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45071</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45685</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45842</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44949</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45842</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45299</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45843</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45139</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45849</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44491</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45849</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44949</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45849</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45734</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45582</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45849</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>46174</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46174</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46174</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46174</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>44984</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45802</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45022</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44525</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45314</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44981</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45699</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45562</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45098</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44964</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44951</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45415</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45222</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45322</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45089</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45555</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45076</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45719</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45485</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45156</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45156</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>44517</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45824</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>46184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45695</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45450</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45096</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45751</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45170</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45343</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45730</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45792</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45093</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44909</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44645</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44977</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45630</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46188</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44483</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44553</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45182</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45363</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45554</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45545</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45555</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45070</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45225</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45730</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45139</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45139</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>44880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45635</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45826</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45275</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44977</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45104</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45184</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45275</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>46191</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45643</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45734</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>46196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46196</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>46209</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46202</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45747</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44802</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>46209</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44600</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>46209</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>44594</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46206</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45646</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44532</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>46251</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45426</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45762</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44600</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46253</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45152</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45132</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>46255</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45195</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45232</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45179</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45688</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45337</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45174</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46259</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44753</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45171</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45385</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45159</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45581</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45707</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45231</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45314</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>46222</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45215</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>46050</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45320</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45230</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45317</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45131</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45268</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44764</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46269</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46135</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>46272</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45035</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44873</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45135</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44901</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45054</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45957</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>46237</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45981</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44882</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45377</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46237</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45232</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44908</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45166</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46286</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>45327</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>44909</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45385</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>46171</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>44964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44774</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>46290</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>44930</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46246</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45357</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44501</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46290</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46246</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46246</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>46290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45603</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>46290</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>44726</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>44726</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45278</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45274</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44942</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45658</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45035</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>44943</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45440</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45320</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45589</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45112</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45112</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45453</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45327</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>44810</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45057</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44949</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44602</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45156</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>44943</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45603</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44909</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45219</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45664</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45098</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45603</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45239</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45303</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45040</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45617</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45130</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>44929</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45075</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45264</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44865</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45206</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45349</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45758</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45246</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45646</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45576</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45538</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45695</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45587</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45644</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44973</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45825</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44879</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44846</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46038</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>46135</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>46051</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46121</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45971</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45730</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         <v>45224</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>44596</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46245</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>46290</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45321</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45159</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44663</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44483</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>44483</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44749</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44469</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44600</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44512</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45625</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45734</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45327</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45688</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>45195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45208</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45364</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44827</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45135</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44771</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45219</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45362</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44810</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44810</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44467</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45119</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45239</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45239</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44869</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>46034</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>46034</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44467</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45020</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45818</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44928</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45337</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44511</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>46038</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45483</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44855</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44873</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>46048</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45903</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45841</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45905</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45905</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46052</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45349</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46056</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>46056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>45548</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45553</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44639</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>46057</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>45918</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>45603</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>45603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>45918</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44501</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>45519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44600</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45364</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45834</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>46078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45320</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45239</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45994</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44943</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>46093</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46091</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45587</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45589</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46094</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>46098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45377</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45089</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>46105</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45006</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>46105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>44895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45282</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>46113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>44831</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45628</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>46121</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44469</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>46122</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45965</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45971</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45973</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45002</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45979</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45646</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>46134</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>46133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45849</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45582</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>46135</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44677</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45845</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44902</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45994</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45076</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45693</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45027</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45035</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45707</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45171</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44846</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45544</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45680</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46006</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>46009</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45727</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>46009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45994</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45006</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45188</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45644</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45769</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45687</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45700</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44902</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45825</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>44603</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45299</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45474</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>46142</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>44928</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46151</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45253</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45385</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45278</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45342</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45342</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45614</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45071</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45685</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45842</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44949</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45842</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45299</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45843</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45139</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45849</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44491</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45849</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44949</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45849</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45734</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45582</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45849</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>46174</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>46174</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46174</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46174</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>44984</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45802</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45022</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>44525</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45314</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>44981</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45699</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45562</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45098</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44964</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>44951</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45415</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45222</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45322</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45089</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45555</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45076</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45719</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45485</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45156</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45156</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>44517</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45824</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>46184</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45695</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45450</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45096</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45751</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45170</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45343</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45730</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45792</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45093</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44909</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44645</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44977</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45630</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46188</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44483</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44553</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45182</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45363</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45554</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>45545</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45555</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45070</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45225</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45730</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45139</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45139</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>44880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45635</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45826</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45275</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44977</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45104</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45184</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45275</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>46191</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45643</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45734</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>46196</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>46196</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>46209</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46202</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46202</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45747</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44802</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>46209</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44600</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>46209</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>44594</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46206</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45646</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>44532</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>46251</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46211</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45426</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45762</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>44600</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46253</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45152</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45132</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>46255</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45195</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45232</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45179</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45688</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45337</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45174</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46259</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44753</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45171</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45385</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>45159</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45581</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45707</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45231</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45314</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>46222</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>45215</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>46050</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45320</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45230</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45317</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45131</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45268</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44764</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>46269</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46135</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>46272</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45035</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44873</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45135</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44901</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45054</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45957</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>46237</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45981</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>44882</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45377</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46237</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45232</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44908</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45166</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46286</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>45327</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>44909</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45385</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>46255</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>46171</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>44964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44774</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>46290</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>44930</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>46246</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45357</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44501</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46290</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46246</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46246</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>46290</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45603</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>46290</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>44726</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>44726</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45278</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45274</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44942</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45658</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45035</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>44943</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45440</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45320</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45589</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45112</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45112</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45453</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45327</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>44810</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>45057</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>44949</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44602</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45156</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>44943</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44883</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>45603</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>44909</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45219</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>45664</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45098</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45603</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45239</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45303</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45040</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45617</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45130</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>44929</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45075</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45264</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>44865</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45206</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45349</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45758</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45246</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45646</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45576</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45538</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45695</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45000</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45587</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45644</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44973</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46135</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45832</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44846</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>46051</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45224</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46121</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45321</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45209</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45730</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46245</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46290</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45159</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44663</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44473</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44483</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>44483</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44749</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44508</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44901</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45112</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45132</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44774</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45057</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44942</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44532</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44802</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45089</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45278</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44726</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45098</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44928</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45630</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45135</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45538</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45377</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44846</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>45264</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45695</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45273</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45231</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46009</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45688</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44943</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45994</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>45818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>45644</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45734</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>46034</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>46034</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45905</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>45905</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44928</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46038</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>46048</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>45253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45719</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45362</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>46052</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45841</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>46056</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>46056</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45834</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>46057</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>44981</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45664</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45385</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45589</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>44501</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45215</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45076</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>46078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45693</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44810</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44908</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44949</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44949</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44753</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45239</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45603</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45440</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45098</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44984</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45959</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>46091</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44901</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45965</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45071</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45385</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>44929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46093</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45020</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45670</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45971</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>46098</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45603</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45349</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45219</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45973</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44600</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>46106</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45979</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>46105</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>46105</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45553</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44603</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>46121</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46122</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45994</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45562</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44865</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45483</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>46133</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44882</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45320</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>46135</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45211</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45035</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45845</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45139</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45027</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45842</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45843</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45707</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45842</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45587</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45299</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45849</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45849</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45849</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45680</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45849</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44883</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45206</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45385</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45734</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45700</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45812</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45035</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45426</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45644</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45519</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44501</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45802</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45299</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45322</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45156</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45555</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45555</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45555</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44977</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45695</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45730</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45730</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45168</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45275</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45225</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45485</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45792</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45824</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>44902</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44951</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45343</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46142</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45222</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44645</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45751</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44483</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44553</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>44880</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45184</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45327</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45617</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45582</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44964</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45450</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45275</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44517</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45156</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45093</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45166</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45104</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45826</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44909</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45363</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45147</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>44951</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45070</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>44977</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>46151</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44600</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45658</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44930</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>46030</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45327</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45020</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45685</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45377</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45131</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45849</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46174</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46174</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>46174</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45727</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45320</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45230</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45179</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44902</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46184</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45119</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45688</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45327</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44831</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45628</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>44511</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>46191</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>46196</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>46196</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45035</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45699</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46202</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44869</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44869</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45002</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>46209</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>46202</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44873</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>44895</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45646</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45219</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44771</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44873</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>46209</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46209</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>46066</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44922</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44827</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>44949</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45232</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45171</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45337</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>46259</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44572</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>46222</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45364</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45006</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45006</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44594</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44525</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46269</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45195</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>46272</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45320</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>46279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44677</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45237</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45195</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45349</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45230</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46237</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>44600</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>46171</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45589</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>46286</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45126</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>46255</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45069</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45314</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45643</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46246</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46246</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45119</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>46246</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44855</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46290</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45208</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>46135</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45139</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45139</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>46290</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46290</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45314</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44639</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>44943</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45342</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45342</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44810</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45054</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46290</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>44511</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45531</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44602</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>46251</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45337</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45268</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45112</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45112</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45040</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45747</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46297</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45135</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45603</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45734</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45707</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44909</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46297</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45357</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45581</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>46297</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46255</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>46297</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>46253</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45174</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45303</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45582</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45474</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45022</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44726</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45075</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>45159</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45239</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45544</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>45603</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45364</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45239</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45282</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45152</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45076</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45317</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45156</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45278</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45603</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45006</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45762</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45188</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45130</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>44491</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45646</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45415</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45548</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45758</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45646</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45246</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45576</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44973</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46135</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45832</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44846</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>46051</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45224</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46121</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>44831</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45321</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45209</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45730</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>46279</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46245</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46290</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45159</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44663</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44473</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44483</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>44483</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44859</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44749</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44873</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44508</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44901</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45112</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45132</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44774</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45057</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44942</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44532</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44802</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45089</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45278</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>44726</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45098</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44928</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45630</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45135</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45538</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45377</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44846</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>45264</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45695</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45273</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45231</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46009</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45688</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44943</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45994</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>45818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>45644</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45734</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>46034</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>46034</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45905</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>45905</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44928</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46038</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>46048</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>45253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45918</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45719</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45362</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>46052</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45841</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>46056</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>46056</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45834</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>46057</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>44981</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45664</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>45385</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45589</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>44501</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45215</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45076</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>46078</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45693</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>44810</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44810</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>44908</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44949</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44949</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44753</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45239</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45603</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45440</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45098</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44984</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45959</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>46091</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44901</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45965</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45071</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45385</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>44929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46093</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45020</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45670</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45971</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>46098</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45603</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45349</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45219</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45973</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>44600</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>46106</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45979</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>46105</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>46105</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45553</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44603</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>46121</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46122</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44909</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45994</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45562</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44865</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45483</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>46133</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>44882</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45320</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>46135</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46134</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45211</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45035</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45845</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45139</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45027</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45842</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45843</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45707</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45842</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45587</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45299</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45849</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45849</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45849</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45680</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45849</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44883</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45206</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45385</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45734</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45700</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45812</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45035</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45426</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45644</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45519</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44501</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45802</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45299</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45322</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45156</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45555</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45555</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45555</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>44977</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45695</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45730</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45730</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45168</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45275</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45170</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45225</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45485</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45792</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45824</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>44902</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44951</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45343</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46142</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45222</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>44645</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45751</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44483</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44553</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>44880</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45184</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45327</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45617</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45582</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44964</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45450</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45275</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44517</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45625</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45156</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45093</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45166</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45104</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45826</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44909</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45363</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45147</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>44951</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45070</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>44977</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>46151</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>44600</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45658</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44930</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>46030</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45327</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45614</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45020</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45685</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45377</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>44764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45131</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45849</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46174</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46174</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>46174</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45727</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45320</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45230</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45179</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44902</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>46184</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45119</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>45688</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45327</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44831</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>45628</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>44511</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>46191</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>46196</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>46196</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>45035</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45699</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46202</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>44869</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>44869</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45002</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>46209</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>46202</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44873</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>44895</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>45646</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>46206</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45219</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44771</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>46206</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44873</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>46211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>46209</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46209</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>46066</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44922</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44827</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>44949</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45232</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45171</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45337</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>46259</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>44572</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>46222</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45364</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45006</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45006</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>44594</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44525</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46269</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45195</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>46272</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45320</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>46279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>46268</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>45957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>45981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44677</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>46237</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45237</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>45195</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45349</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45230</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46237</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>44600</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>46171</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45589</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>46286</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45126</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>46255</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>45069</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45314</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45643</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>46246</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46246</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45119</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>46246</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>46288</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44855</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46290</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>45208</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>46135</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45139</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>45139</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>46290</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>46290</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45314</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44639</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>44943</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45342</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45342</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>44810</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45054</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46290</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>44511</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45531</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44602</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>46251</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45337</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45268</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45112</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45112</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>45040</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45747</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46297</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45135</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45603</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45734</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45707</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44909</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46297</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45357</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45581</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>46297</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46255</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>46297</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>46253</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45174</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45303</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>45582</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45474</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45022</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>44726</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45075</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>45159</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45239</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45544</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>45603</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45364</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45239</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45282</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45152</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45076</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45317</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45156</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45278</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45603</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45006</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45762</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45188</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45130</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>44491</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45646</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45415</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45548</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45758</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45646</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45246</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45576</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44973</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44846</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>45832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46133</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>46135</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>46038</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45321</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45159</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45812</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45224</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44802</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45730</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>46121</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45146</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>46279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>46245</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45971</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44663</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44483</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44746</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>44600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44537</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44749</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44698</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44859</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44553</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45364</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45135</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44771</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44928</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45625</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45362</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45156</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45385</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45327</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45278</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45342</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44883</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45342</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45603</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44909</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45688</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>44810</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45071</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44949</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45208</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45230</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45237</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44491</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44949</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45098</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45603</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45239</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45303</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45040</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45818</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45239</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45239</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45130</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44984</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44869</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44869</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45075</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44922</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45020</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45264</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44928</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45337</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44865</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>45206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44511</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44511</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45022</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45112</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45314</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45483</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45905</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44855</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45349</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45905</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44981</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45905</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45098</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44873</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45699</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45126</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45562</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45098</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45415</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45758</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45076</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45719</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45918</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45349</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45553</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45630</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44639</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45182</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>45246</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45603</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45139</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45139</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45646</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45576</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44501</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45519</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45695</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44600</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45273</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45643</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45000</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45364</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45644</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45834</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45734</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45531</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45582</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45747</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44572</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44802</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45589</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44600</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44594</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45377</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45646</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45089</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45119</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44532</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45006</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45006</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45426</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45762</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45282</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45020</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45152</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45132</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45232</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45179</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45688</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45628</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45093</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45174</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>44909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45825</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45670</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44753</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45959</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45171</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45211</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45385</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45002</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45159</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45646</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45707</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45231</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45842</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45842</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45299</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45843</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45314</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45849</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45973</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45849</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45849</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44677</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45076</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45693</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45215</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45734</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45320</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45707</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45230</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45317</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45131</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45802</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44846</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45544</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45268</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44764</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>44964</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>44902</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45222</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45322</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45089</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45555</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45485</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45156</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45156</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44517</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45824</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45695</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45450</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45096</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45168</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45751</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45170</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45343</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45730</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45792</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45093</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44951</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44909</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44645</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>44977</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44483</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>44553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45363</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45554</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45555</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45070</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45225</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45730</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>44880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45635</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45035</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45826</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45275</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45979</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44977</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45147</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45104</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45275</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45006</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45188</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>44873</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46094</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45687</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46098</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45135</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44901</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44902</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45054</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44882</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45377</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>46105</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45232</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44603</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45474</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46106</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>46111</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44908</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45166</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45327</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45994</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44909</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>46121</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45385</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46122</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>44964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46134</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46133</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>46006</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45849</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44774</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46135</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44930</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45357</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>44501</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>46009</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46009</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45845</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44902</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45994</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45603</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45027</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44726</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>44726</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45035</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45278</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45274</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44942</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45680</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45658</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>46034</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>46034</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>45035</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44943</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45812</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45440</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45320</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>46038</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45589</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45112</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45112</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45644</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45453</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46048</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45327</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>44810</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45057</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45195</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44949</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45299</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46052</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46056</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46056</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46142</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46057</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>46151</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>46078</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45239</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>46030</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45994</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46093</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46091</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45614</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45685</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45849</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46174</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46174</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46174</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46174</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46184</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>46191</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>46196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46196</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46209</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46202</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>46202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>46209</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>46209</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46206</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46211</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45337</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>46066</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46222</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46050</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46269</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46272</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46237</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46279</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>46237</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46286</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>46255</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>46171</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46290</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>46246</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>46290</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>46246</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>46246</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>46290</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46290</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46135</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>46253</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46297</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45903</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>46297</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46297</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>46255</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46259</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45957</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44973</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44846</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>45832</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46133</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>46135</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>46038</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44831</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45321</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45159</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45812</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45224</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44802</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45730</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44596</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>46121</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45146</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>46051</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>46279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>46245</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>46290</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45971</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45460</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45552</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45727</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44526</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45880</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46062</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>46134</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44749</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44663</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44483</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44746</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>44600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44537</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44749</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44698</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44859</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44553</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44491</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44508</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45364</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45135</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44771</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44928</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45625</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45362</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45156</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45385</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45327</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45278</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45342</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44883</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45342</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45603</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44909</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45688</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>44810</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45071</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44949</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45139</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45208</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45230</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45237</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44491</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44949</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45098</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45603</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45239</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45303</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45040</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45818</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45239</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45239</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45130</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44984</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44869</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44869</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44929</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45075</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44922</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45020</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45264</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44928</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45337</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44865</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>45206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44511</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44511</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45022</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45112</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>45314</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>45483</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45905</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44855</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45349</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45905</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44981</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45905</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45098</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44873</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45699</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45126</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>45562</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45098</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45415</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45758</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45076</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45719</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45918</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45918</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45349</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45548</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45553</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45630</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44639</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45182</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>45246</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45603</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45139</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45139</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45646</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45576</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44501</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45519</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45538</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45695</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44600</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45273</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>45643</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45000</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45364</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45644</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45834</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45734</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45320</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45531</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>45582</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44943</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45747</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44572</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44802</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45589</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44600</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>44594</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45377</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45646</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45089</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45119</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44532</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45006</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45006</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45426</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45762</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>44895</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>44600</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45282</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45020</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45152</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45132</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>44831</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45232</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45179</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45688</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45628</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45093</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45174</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>44909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45825</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45670</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44753</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>45959</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45171</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45211</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45385</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45002</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45159</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45646</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45707</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45231</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45842</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45842</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45299</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45843</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45314</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45582</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45973</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45849</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45973</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45849</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45849</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>44677</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45076</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45693</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45215</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45734</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45320</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45707</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45230</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45317</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45131</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45802</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>44846</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45544</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45268</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44764</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>44964</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>44902</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45222</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45322</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45089</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45555</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45485</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45156</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45156</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44517</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45824</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45695</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45450</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45096</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45168</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45751</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45170</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45343</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45730</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45792</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45093</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44951</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44909</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44645</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>44977</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44483</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>44553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45363</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45554</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45555</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45070</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45225</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45730</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>44880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45635</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45035</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45826</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45275</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>44964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45979</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44977</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45147</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45104</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45184</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45275</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45006</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45188</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>44873</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>46094</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45687</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>46098</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45135</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44901</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44902</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45054</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44882</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45377</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>46105</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45232</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44603</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45474</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46106</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>46111</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>44908</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45166</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45327</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45994</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44909</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>46121</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45385</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46122</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>44964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46134</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46133</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>46006</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45849</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44774</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>46135</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44930</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45357</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>44501</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>46009</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46009</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45845</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44902</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45994</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45603</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45027</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44726</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>44726</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45035</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45278</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45274</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44942</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45680</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45658</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>46034</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>46034</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>45035</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44943</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45812</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45440</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>45320</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>46038</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45589</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45112</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45112</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45644</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45453</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>46048</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45327</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>44810</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45057</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45195</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44949</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45841</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45299</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>46052</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46056</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46056</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>46142</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>46057</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>46151</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>46078</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45239</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>46030</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45994</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46093</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46091</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45614</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45685</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>45849</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46174</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46174</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46174</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46174</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46174</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46184</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>46191</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>46196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46196</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46209</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46202</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>46202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>46209</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>46206</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>46209</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>46206</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>46211</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45337</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>46066</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46222</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46050</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46269</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46272</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46237</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46279</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>46237</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46286</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>46255</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>46171</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46290</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>46246</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34438,7 +34438,7 @@
         <v>46290</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34511,7 +34511,7 @@
         <v>46246</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>46246</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>46290</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>46290</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>46288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46135</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34949,7 +34949,7 @@
         <v>46253</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>46297</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46297</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45903</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>46297</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46297</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>46255</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35533,7 +35533,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46259</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45957</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45265</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46038</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46135</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45224</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45321</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46051</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46121</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45146</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>46245</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45159</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46290</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45730</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45727</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>44526</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45880</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46062</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46134</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44663</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44859</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44537</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44698</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44873</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44600</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44508</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44901</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45687</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45089</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44942</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44532</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44802</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44774</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>45098</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44928</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>44726</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45630</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45135</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45182</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45377</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>44846</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>45264</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45093</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45231</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45688</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44943</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44909</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45734</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45253</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45362</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45719</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45385</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>44501</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45215</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45582</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44753</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45693</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45603</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45440</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>44810</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45098</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>44949</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44949</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44984</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45385</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45020</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45071</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44929</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45670</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45349</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45553</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45849</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45680</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44603</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44909</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45818</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45562</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45700</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45812</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44865</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45483</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44943</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44882</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45320</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45644</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45195</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45232</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45299</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45211</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45905</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45905</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45905</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45139</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46142</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45918</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45707</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45918</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45834</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45206</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>46151</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45385</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45426</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45098</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46030</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44501</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45614</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45965</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45453</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45971</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45971</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>45973</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45973</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45327</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45617</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45582</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44600</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45658</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44930</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45327</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45377</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45994</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44764</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>46174</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45131</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46009</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46009</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46174</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46174</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46174</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45727</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45994</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45994</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45320</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45230</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45179</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>44902</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45119</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46038</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45688</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45327</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46048</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45628</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44511</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45035</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46052</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45841</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46056</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>46184</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46057</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45699</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44869</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44869</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46188</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45002</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>44873</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45646</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45239</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45219</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>44771</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44873</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>46091</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44922</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44827</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46094</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>46093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44949</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>46191</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45232</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45171</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46196</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46098</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>46106</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46105</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>46105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44572</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46111</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45364</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>46113</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45006</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45006</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46202</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46121</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44594</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46122</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44525</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>46209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46202</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45195</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>46133</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46135</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45320</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46134</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>44677</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45035</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45237</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45845</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45195</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45349</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45230</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>46206</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45027</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44600</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46206</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45589</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>46211</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>46209</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46066</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45337</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45314</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>46222</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45643</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>46050</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45119</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46272</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44855</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45208</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45139</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45139</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45314</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44639</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44943</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45342</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45342</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44810</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45054</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44511</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>46279</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45531</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>44602</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>46237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45337</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45268</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45112</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45112</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45040</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>46237</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45135</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45603</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45734</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>46171</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45707</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>44909</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>45357</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45581</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>46286</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45174</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45303</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45582</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45474</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>45022</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>46246</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>44726</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>46246</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45075</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45159</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45544</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46246</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45603</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45364</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46290</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45239</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46135</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>45152</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>46290</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>45076</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>45317</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45156</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45278</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45603</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45006</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>46251</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45762</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45188</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45130</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>46297</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>46297</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44491</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>46297</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>46255</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46297</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45646</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45415</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45548</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45758</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45903</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45646</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45981</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45246</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45576</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45538</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>46303</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46259</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45695</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45273</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45587</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45644</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45000</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46307</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>46307</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46255</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>46269</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46311</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>46268</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45171</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45825</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>46311</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45842</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45843</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45842</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45299</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45849</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45849</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45849</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45734</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45802</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45322</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45156</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45635</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45555</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45555</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45555</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44977</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45554</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45545</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45695</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45730</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45730</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45096</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45275</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45170</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45089</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45485</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45792</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45824</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>44902</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44951</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45343</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45222</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44645</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45751</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44553</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>44880</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45104</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>44964</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45450</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45275</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44517</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45156</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45093</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45104</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45826</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>44909</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45363</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45147</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44951</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45070</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44977</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>45400</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45265</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46038</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46135</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>46133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45832</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45224</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45321</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46051</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46121</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45146</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>46245</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45159</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46290</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45812</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45209</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>45730</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45727</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>44526</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45880</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46062</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46134</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44663</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44859</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44537</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44749</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44698</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44873</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44600</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44508</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44901</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45687</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45089</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44942</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44532</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44802</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44774</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45112</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>45098</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44928</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>44726</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45630</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45135</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45182</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45377</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>44846</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>45264</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45093</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45231</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45688</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44943</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44909</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45734</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45253</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45362</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45719</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45385</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>44501</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45215</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45076</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45582</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45664</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45274</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44753</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>45693</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>45603</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>45440</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>44810</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>45098</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>44949</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44949</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44984</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44901</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45385</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45020</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45071</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44929</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45670</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45349</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45553</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45849</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45680</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44603</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44909</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45818</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45562</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45700</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45812</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44865</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45483</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44943</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44882</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45320</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45644</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45195</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45232</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45299</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45211</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45905</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45905</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45905</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45139</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>46142</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45918</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45707</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45918</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45834</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>44883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45206</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>46151</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45385</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45035</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45426</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45098</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46030</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>44501</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45614</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45965</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>45453</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45971</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45971</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>45973</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45973</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45327</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45617</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45582</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45625</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>44600</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45658</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44930</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45327</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>45020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45377</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45994</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>44764</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>46174</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45131</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46009</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>46009</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46174</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46174</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46174</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45727</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45994</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45994</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45320</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45230</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45179</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>44902</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45119</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46038</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45688</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45327</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44831</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46048</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45628</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44511</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45035</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46052</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45841</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46056</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>46184</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46057</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45699</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44869</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44869</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46188</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45002</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>44873</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45646</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45239</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45219</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>44771</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44873</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>46091</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44922</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44827</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46094</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>46093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44949</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>46191</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45232</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45171</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>46196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>46196</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46098</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>46106</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>46105</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>46105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44572</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46111</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45364</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>46113</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45006</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45006</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>46202</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46121</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44594</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46122</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44525</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>46209</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46202</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45195</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>46133</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46135</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45320</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46134</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>44677</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45035</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45237</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45845</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45195</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45349</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45230</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>46206</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45027</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44600</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46206</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45589</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>46211</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>46209</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46066</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45337</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45069</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45314</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>46222</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45643</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>46050</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45119</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46272</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44855</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45208</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45139</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45139</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45314</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44639</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>44943</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45342</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>45342</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44810</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45054</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44511</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>46279</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45531</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>44602</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>46237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45337</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45268</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45112</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45112</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45040</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45747</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>46237</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45135</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45603</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45734</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>46171</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45707</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>44909</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>45357</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45581</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>46286</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45174</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45303</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45582</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45474</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>45022</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>45211</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>46246</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>44726</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>46246</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45075</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45159</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45239</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>45544</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46246</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45603</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45364</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>46290</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>45239</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46135</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46290</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46290</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45282</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>45152</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>46290</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>45076</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>45317</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>45156</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45278</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45603</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45006</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>46251</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45762</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45188</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45130</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>46297</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>46297</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44491</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>46297</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>46255</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>46297</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45646</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45415</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>45548</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45758</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>45903</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45646</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>45981</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45246</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45576</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45538</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>46303</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>46259</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45695</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45273</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45587</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45644</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45000</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>46307</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>46307</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46255</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>46269</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46311</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>46268</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45171</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45825</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>46311</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45842</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45843</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31988,7 +31988,7 @@
         <v>45842</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45299</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45849</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45849</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45849</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45734</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45802</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45322</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45156</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45635</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45555</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45555</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45555</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>44977</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45554</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45545</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45695</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45730</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45730</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45096</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45275</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>45170</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>45089</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45485</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45792</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45824</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>44902</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44951</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45343</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45222</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44645</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45751</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44553</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>44880</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45104</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>44964</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45450</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45275</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44517</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45156</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45093</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45104</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45826</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>44909</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45363</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45147</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>44951</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45070</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44977</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45442</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44517</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>44931</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45635</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45799</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45950</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>46091</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>46094</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>46098</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46288</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>44973</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45400</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>44846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45832</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>46133</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>46135</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45321</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45159</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45680</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46290</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45971</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46121</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45209</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45730</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44928</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45727</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>44526</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45880</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46062</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46134</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44663</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44859</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44537</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44600</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44698</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44873</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44727</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45818</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>45327</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45688</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44774</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>45357</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45208</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45603</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45905</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44726</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44726</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45905</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45614</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45274</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45685</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44942</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45658</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45035</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45440</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45320</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45364</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45589</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>45112</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45112</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>45834</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45135</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44771</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45849</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45453</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45362</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>46174</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45327</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45057</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>46174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>46174</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>46174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44602</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44810</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44810</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45156</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44883</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45603</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44909</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>46184</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45959</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>46188</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>45971</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45664</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45098</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>46196</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>46196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45973</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45239</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45303</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45119</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45040</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45979</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45617</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45130</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46209</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>46206</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46206</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44929</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45075</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46211</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45264</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44865</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45206</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45994</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45337</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46066</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45349</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46222</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>46050</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45758</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>46006</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46009</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46009</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45994</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45994</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45246</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>46279</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45646</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45576</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45538</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45695</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46286</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46034</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45587</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45644</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46034</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>46038</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46290</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>46052</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46056</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>46056</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>46246</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>46246</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>46290</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>46057</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>46290</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>46135</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45171</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>46251</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>46078</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45825</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45239</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46297</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46093</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46297</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45903</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46094</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46297</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46098</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45842</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45842</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45299</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46297</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46255</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45843</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44869</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44869</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44922</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45981</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45849</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45849</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45849</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46106</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45734</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46111</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>46113</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46259</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45337</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45802</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44511</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44511</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44902</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44951</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45104</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45222</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45322</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45089</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>46121</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45555</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45485</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45156</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45156</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44517</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>46122</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45695</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45450</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45096</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45168</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45751</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45170</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45343</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45730</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45792</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45093</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>44951</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>44909</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>44645</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44977</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44553</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45363</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45554</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45545</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45555</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45070</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45225</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45730</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44880</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45635</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45826</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45555</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>45275</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>44964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44977</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45147</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45104</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45184</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45275</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46303</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46307</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>46307</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45483</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>46134</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>46133</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45849</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46135</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45349</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45548</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45553</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44639</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45845</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>44902</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>46255</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45603</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45603</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46268</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>46311</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45027</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>46311</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44501</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45519</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45680</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>44600</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45812</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45364</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>46272</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45644</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45320</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45700</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45582</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45195</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45299</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>46142</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44943</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44572</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45587</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45589</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45377</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45089</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>46151</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45006</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45006</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>44895</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>46030</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45282</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45020</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44831</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45628</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>44909</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45002</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45646</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45582</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44677</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45076</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>45693</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45707</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44846</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45544</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45727</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45006</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45687</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>44902</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44603</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45474</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45385</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45278</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45342</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>45342</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45071</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44949</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45069</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45139</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45237</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>44949</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45582</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44984</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45022</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44525</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45112</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45314</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>44981</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45699</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45126</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45562</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45098</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45415</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45076</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45719</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45630</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45182</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45139</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45139</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45643</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45734</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45531</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45747</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44802</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>44600</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44594</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45646</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44532</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45426</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45762</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44600</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45152</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45195</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>45232</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45179</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>45688</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45174</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45670</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>44753</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45171</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45195</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45211</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>45385</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45159</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>45581</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45707</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45231</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45314</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>45215</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45320</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45230</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45317</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45131</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45268</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44764</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44873</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45135</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45054</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44882</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45377</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45232</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45166</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45327</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>44909</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45385</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44964</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45442</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44992</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44995</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44517</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>44931</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45635</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45799</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45880</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45950</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46035</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46072</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>46091</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46091</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>46094</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46098</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>46288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>

--- a/Översikt LAHOLM.xlsx
+++ b/Översikt LAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44634</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>46171</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>46136</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45819</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>44973</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>45400</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46094</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>44879</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45356</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45735</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>44846</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45832</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>46133</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>46135</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>44831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45321</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45159</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45680</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46051</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46290</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>45971</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46121</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>45209</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>45730</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44928</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45224</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44802</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45460</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45552</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>45727</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>44526</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45880</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46062</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>46120</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46134</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44749</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44663</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44678</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44746</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>44859</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44537</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44600</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44749</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44698</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44698</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44873</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44600</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44727</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44508</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45818</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>45327</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45688</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44774</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>45357</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44501</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45208</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45230</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>45603</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45905</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44726</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44726</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>45905</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45905</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>45614</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45278</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45274</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45685</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44942</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45658</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45035</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45440</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45320</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>45364</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45589</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>45112</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45112</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>45834</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45135</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44771</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45849</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45453</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45362</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>46174</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45327</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44810</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45057</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>46174</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>46174</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>46174</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>46174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44602</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44810</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44810</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44901</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45156</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44883</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45603</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44909</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>46184</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45959</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>46188</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>46191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>45971</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>45664</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45098</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>46196</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>46196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45973</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45239</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45303</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45119</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>46202</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45040</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45979</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46202</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45617</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45130</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46209</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>46206</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46206</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44929</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45075</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46211</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45264</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44865</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45206</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45994</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45337</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46066</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45349</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46222</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>46050</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45758</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>46006</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46009</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46009</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45994</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45994</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45246</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>46279</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45646</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45576</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45538</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45695</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46286</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46034</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45587</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45644</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46034</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>46038</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>46290</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>46052</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46056</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>46056</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>46246</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>46246</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>46290</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>46057</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>46290</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>46135</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45171</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>46251</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>46078</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45825</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45239</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46297</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46093</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46297</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45903</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46094</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46297</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46098</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45842</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>45842</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45299</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46297</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46255</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45843</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46105</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44869</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44869</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44922</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45981</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45849</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45849</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45849</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46106</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45734</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46111</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>46113</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46259</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44928</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45337</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45802</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44511</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44511</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44902</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44951</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45104</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45222</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45322</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45089</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>46121</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45555</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45485</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45156</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45156</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44517</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>46122</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45695</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45450</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45096</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45168</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45751</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45170</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45343</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45730</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45792</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45093</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>44951</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>44909</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>44645</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44977</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44553</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45363</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45554</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45545</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45555</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45070</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45225</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>45730</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44880</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>45635</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>45826</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45555</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>45275</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>44964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44977</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45147</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>45104</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45184</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45275</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46303</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46307</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>46307</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45483</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44855</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>46134</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>46133</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45849</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46135</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45349</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45548</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45553</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44639</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45845</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>44902</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>46255</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45603</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45603</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46268</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>46311</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45027</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45035</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>46311</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44501</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45519</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45680</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>44600</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45812</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45364</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>46272</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45644</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45320</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45700</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45582</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45195</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45299</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>46142</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44943</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44572</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45587</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45589</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45377</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45089</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>46151</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45006</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45006</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>44895</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>46030</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45282</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45020</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44831</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28298,7 +28298,7 @@
         <v>45628</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>44909</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>45002</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45646</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45582</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44677</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>45076</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>45693</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45707</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44846</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45544</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45727</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45006</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>45687</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>44902</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44603</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45474</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>45253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45385</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45278</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45342</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>45342</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45071</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44949</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45069</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45139</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45237</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>44949</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45582</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44984</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45022</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44525</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45112</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45314</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>44981</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45699</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45126</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45562</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45098</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45415</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45076</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45719</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45630</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45182</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45139</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45139</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45643</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45734</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45531</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45747</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44802</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>44600</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44594</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45646</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44532</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45426</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>45762</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>44600</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>45152</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>45132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45195</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32990,7 +32990,7 @@
         <v>45232</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45179</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>45688</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>45174</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45670</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>44753</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45171</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45195</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45211</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>45385</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45159</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>45581</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45707</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>45231</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45314</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>45215</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>45320</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45230</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45317</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45131</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45268</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44764</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44873</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45135</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44901</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45054</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>44882</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45377</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45232</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45166</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45327</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>44909</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45385</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44964</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>45442</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44992</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>44995</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44517</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>44931</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45635</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45799</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45880</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45950</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46035</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46072</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>46091</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46091</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>46094</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>46098</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>46288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
